--- a/data/samples/helios_data_platform.xlsx
+++ b/data/samples/helios_data_platform.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S40"/>
+  <dimension ref="A1:V40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,6 +507,21 @@
           <t>Actual Finish date</t>
         </is>
       </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Effort (hours)</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Effort completed (hours)</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Effort remaining (hours)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -539,12 +554,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>C. Meyer</t>
+          <t>E. Novak</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -567,7 +582,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -577,7 +592,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -587,8 +602,17 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
-        </is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>56</v>
+      </c>
+      <c r="U2" t="n">
+        <v>56</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -604,7 +628,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>A. Silva</t>
+          <t>H. Costa</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -622,7 +646,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -632,7 +656,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -642,7 +666,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -652,8 +676,17 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
-        </is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>40</v>
+      </c>
+      <c r="U3" t="n">
+        <v>40</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -679,12 +712,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>E. Novak</t>
+          <t>C. Meyer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -697,7 +730,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -707,7 +740,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -717,7 +750,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -727,8 +760,17 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>24</v>
+      </c>
+      <c r="U4" t="n">
+        <v>24</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -754,7 +796,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P. Ahmed</t>
+          <t>A. Silva</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -802,8 +844,17 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
-        </is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>60</v>
+      </c>
+      <c r="U5" t="n">
+        <v>60</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -819,12 +870,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>T. Bauer</t>
+          <t>F. Lindqvist</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -837,7 +888,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -857,7 +908,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -867,8 +918,17 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
-        </is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>60</v>
+      </c>
+      <c r="U6" t="n">
+        <v>60</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -902,12 +962,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>F. Lindqvist</t>
+          <t>N. Kaur</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -940,7 +1000,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -952,6 +1012,15 @@
         <is>
           <t>2026-04-18</t>
         </is>
+      </c>
+      <c r="T7" t="n">
+        <v>16</v>
+      </c>
+      <c r="U7" t="n">
+        <v>16</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -982,7 +1051,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1015,7 +1084,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1025,8 +1094,17 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
-        </is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>16</v>
+      </c>
+      <c r="U8" t="n">
+        <v>16</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1052,7 +1130,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>C. Meyer</t>
+          <t>E. Novak</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1070,7 +1148,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1080,7 +1158,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1100,8 +1178,17 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
-        </is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="T9" t="n">
+        <v>24</v>
+      </c>
+      <c r="U9" t="n">
+        <v>24</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1117,12 +1204,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>A. Silva</t>
+          <t>H. Costa</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1165,11 +1252,28 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
-        </is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="T10" t="n">
+        <v>24</v>
+      </c>
+      <c r="U10" t="n">
+        <v>24</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Approved Budget</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>210000</v>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2.1</t>
@@ -1182,12 +1286,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>E. Novak</t>
+          <t>C. Meyer</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1210,7 +1314,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1220,7 +1324,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1230,8 +1334,17 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
-        </is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
+        <v>112</v>
+      </c>
+      <c r="U11" t="n">
+        <v>112</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1255,12 +1368,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P. Ahmed</t>
+          <t>A. Silva</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1269,7 +1382,7 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1300,6 +1413,15 @@
         <is>
           <t>2026-05-04</t>
         </is>
+      </c>
+      <c r="T12" t="n">
+        <v>24</v>
+      </c>
+      <c r="U12" t="n">
+        <v>10</v>
+      </c>
+      <c r="V12" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -1315,12 +1437,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>T. Bauer</t>
+          <t>F. Lindqvist</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1329,11 +1451,11 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1343,7 +1465,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1353,13 +1475,22 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
           <t>2026-05-09</t>
         </is>
+      </c>
+      <c r="T13" t="n">
+        <v>80</v>
+      </c>
+      <c r="U13" t="n">
+        <v>8</v>
+      </c>
+      <c r="V13" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="14">
@@ -1375,12 +1506,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>F. Lindqvist</t>
+          <t>N. Kaur</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1389,7 +1520,7 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1413,13 +1544,22 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
           <t>2026-05-15</t>
         </is>
+      </c>
+      <c r="T14" t="n">
+        <v>48</v>
+      </c>
+      <c r="U14" t="n">
+        <v>21</v>
+      </c>
+      <c r="V14" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -1440,7 +1580,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1475,6 +1615,15 @@
         <is>
           <t>2026-05-20</t>
         </is>
+      </c>
+      <c r="T15" t="n">
+        <v>160</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>160</v>
       </c>
     </row>
     <row r="16">
@@ -1490,12 +1639,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>C. Meyer</t>
+          <t>E. Novak</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1530,6 +1679,15 @@
         <is>
           <t>2026-05-26</t>
         </is>
+      </c>
+      <c r="T16" t="n">
+        <v>336</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>336</v>
       </c>
     </row>
     <row r="17">
@@ -1545,7 +1703,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>A. Silva</t>
+          <t>H. Costa</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1563,7 +1721,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1585,6 +1743,15 @@
         <is>
           <t>2026-05-31</t>
         </is>
+      </c>
+      <c r="T17" t="n">
+        <v>96</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>96</v>
       </c>
     </row>
     <row r="18">
@@ -1600,7 +1767,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>E. Novak</t>
+          <t>C. Meyer</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1618,7 +1785,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1640,6 +1807,15 @@
         <is>
           <t>2026-06-05</t>
         </is>
+      </c>
+      <c r="T18" t="n">
+        <v>48</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="19">
@@ -1663,12 +1839,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>P. Ahmed</t>
+          <t>A. Silva</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1681,7 +1857,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1703,6 +1879,15 @@
         <is>
           <t>2026-06-11</t>
         </is>
+      </c>
+      <c r="T19" t="n">
+        <v>64</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="20">
@@ -1718,12 +1903,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>T. Bauer</t>
+          <t>F. Lindqvist</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1736,7 +1921,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1758,6 +1943,15 @@
         <is>
           <t>2026-06-16</t>
         </is>
+      </c>
+      <c r="T20" t="n">
+        <v>200</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="21">
@@ -1773,12 +1967,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>F. Lindqvist</t>
+          <t>N. Kaur</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1791,7 +1985,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1813,6 +2007,15 @@
         <is>
           <t>2026-06-22</t>
         </is>
+      </c>
+      <c r="T21" t="n">
+        <v>120</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="22">
@@ -1833,7 +2036,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1868,6 +2071,15 @@
         <is>
           <t>2026-06-27</t>
         </is>
+      </c>
+      <c r="T22" t="n">
+        <v>48</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="23">
@@ -1883,7 +2095,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>C. Meyer</t>
+          <t>E. Novak</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1923,6 +2135,15 @@
         <is>
           <t>2026-07-03</t>
         </is>
+      </c>
+      <c r="T23" t="n">
+        <v>120</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="24">
@@ -1946,12 +2167,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>A. Silva</t>
+          <t>H. Costa</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1986,6 +2207,15 @@
         <is>
           <t>2026-07-08</t>
         </is>
+      </c>
+      <c r="T24" t="n">
+        <v>96</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>96</v>
       </c>
     </row>
     <row r="25">
@@ -2001,7 +2231,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>E. Novak</t>
+          <t>C. Meyer</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2019,7 +2249,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2029,7 +2259,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2041,6 +2271,15 @@
         <is>
           <t>2026-07-14</t>
         </is>
+      </c>
+      <c r="T25" t="n">
+        <v>48</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="26">
@@ -2056,12 +2295,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>P. Ahmed</t>
+          <t>A. Silva</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2084,7 +2323,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2096,6 +2335,15 @@
         <is>
           <t>2026-07-19</t>
         </is>
+      </c>
+      <c r="T26" t="n">
+        <v>240</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>240</v>
       </c>
     </row>
     <row r="27">
@@ -2111,12 +2359,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>T. Bauer</t>
+          <t>F. Lindqvist</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2129,7 +2377,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2151,6 +2399,15 @@
         <is>
           <t>2026-07-25</t>
         </is>
+      </c>
+      <c r="T27" t="n">
+        <v>180</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>180</v>
       </c>
     </row>
     <row r="28">
@@ -2166,12 +2423,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>F. Lindqvist</t>
+          <t>N. Kaur</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2184,7 +2441,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2206,6 +2463,15 @@
         <is>
           <t>2026-07-30</t>
         </is>
+      </c>
+      <c r="T28" t="n">
+        <v>80</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="29">
@@ -2226,7 +2492,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2261,6 +2527,15 @@
         <is>
           <t>2026-08-05</t>
         </is>
+      </c>
+      <c r="T29" t="n">
+        <v>336</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>336</v>
       </c>
     </row>
     <row r="30">
@@ -2276,12 +2551,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>C. Meyer</t>
+          <t>E. Novak</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2304,7 +2579,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -2316,6 +2591,15 @@
         <is>
           <t>2026-08-10</t>
         </is>
+      </c>
+      <c r="T30" t="n">
+        <v>448</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>448</v>
       </c>
     </row>
     <row r="31">
@@ -2339,12 +2623,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>A. Silva</t>
+          <t>H. Costa</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2357,7 +2641,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2379,6 +2663,15 @@
         <is>
           <t>2026-08-16</t>
         </is>
+      </c>
+      <c r="T31" t="n">
+        <v>180</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>180</v>
       </c>
     </row>
     <row r="32">
@@ -2394,7 +2687,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>E. Novak</t>
+          <t>C. Meyer</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2422,7 +2715,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -2434,6 +2727,15 @@
         <is>
           <t>2026-08-21</t>
         </is>
+      </c>
+      <c r="T32" t="n">
+        <v>64</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="33">
@@ -2449,12 +2751,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>P. Ahmed</t>
+          <t>A. Silva</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2489,6 +2791,15 @@
         <is>
           <t>2026-08-26</t>
         </is>
+      </c>
+      <c r="T33" t="n">
+        <v>560</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>560</v>
       </c>
     </row>
     <row r="34">
@@ -2504,12 +2815,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>T. Bauer</t>
+          <t>F. Lindqvist</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2544,6 +2855,15 @@
         <is>
           <t>2026-09-01</t>
         </is>
+      </c>
+      <c r="T34" t="n">
+        <v>134</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>134</v>
       </c>
     </row>
     <row r="35">
@@ -2559,7 +2879,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>F. Lindqvist</t>
+          <t>N. Kaur</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2587,7 +2907,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -2599,6 +2919,15 @@
         <is>
           <t>2026-09-06</t>
         </is>
+      </c>
+      <c r="T35" t="n">
+        <v>336</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>336</v>
       </c>
     </row>
     <row r="36">
@@ -2650,7 +2979,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -2662,6 +2991,15 @@
         <is>
           <t>2026-09-12</t>
         </is>
+      </c>
+      <c r="T36" t="n">
+        <v>179</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>179</v>
       </c>
     </row>
     <row r="37">
@@ -2677,12 +3015,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>C. Meyer</t>
+          <t>E. Novak</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2695,7 +3033,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2705,7 +3043,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -2717,6 +3055,15 @@
         <is>
           <t>2026-09-17</t>
         </is>
+      </c>
+      <c r="T37" t="n">
+        <v>120</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="38">
@@ -2732,12 +3079,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>A. Silva</t>
+          <t>H. Costa</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2772,6 +3119,15 @@
         <is>
           <t>2026-09-23</t>
         </is>
+      </c>
+      <c r="T38" t="n">
+        <v>160</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>160</v>
       </c>
     </row>
     <row r="39">
@@ -2787,7 +3143,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>E. Novak</t>
+          <t>C. Meyer</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2815,7 +3171,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -2827,6 +3183,15 @@
         <is>
           <t>2026-09-28</t>
         </is>
+      </c>
+      <c r="T39" t="n">
+        <v>48</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="40">
@@ -2842,12 +3207,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>P. Ahmed</t>
+          <t>A. Silva</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2870,7 +3235,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -2882,6 +3247,15 @@
         <is>
           <t>2026-10-04</t>
         </is>
+      </c>
+      <c r="T40" t="n">
+        <v>96</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
